--- a/calculators/token-cost-calculator.xlsx
+++ b/calculators/token-cost-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RajuAr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C8BAE8-D5BD-4024-973F-310FF2A0ACD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308053BD-1CF1-4A28-81ED-14B834D348E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>Input tokens per transaction</t>
   </si>
   <si>
-    <t>Everything you send: the question, the system instructions, retrieved documents, conversation history. A token is about 0.75 of a word.</t>
-  </si>
-  <si>
     <t>Output tokens per transaction</t>
   </si>
   <si>
@@ -329,6 +326,9 @@
   </si>
   <si>
     <t>Provided under the MIT Licence. This is a procurement and commercial tool, not legal advice.</t>
+  </si>
+  <si>
+    <t>Everything you send: the question, the system instructions, retrieved documents, conversation history. A token is about 0.75 of a word (4 characters).</t>
   </si>
 </sst>
 </file>
@@ -856,7 +856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:4" ht="34.5" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
@@ -864,125 +864,125 @@
         <v>8100</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="21">
         <v>400</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C15" s="21">
         <v>2000</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
     </row>
     <row r="18" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="22">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="22">
         <v>15</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
     </row>
-    <row r="22" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" ht="46" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="C22" s="23">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="24">
         <v>0.1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C24" s="23">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="24">
         <v>0.5</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="23">
         <v>0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -1011,7 +1011,7 @@
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="5">
         <f>Inputs!$C$12*Inputs!$C$13/1000000</f>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="5">
         <f>Inputs!$C$12*Inputs!$C$14/1000000</f>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5">
         <f>Inputs!$C$12*Inputs!$C$15/1000000</f>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(C6:C8)</f>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -1083,64 +1083,64 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9">
         <f>C6*Inputs!$C$18*((1-Inputs!$C$22)+Inputs!$C$22*Inputs!$C$23)*(1-Inputs!$C$24*Inputs!$C$25)*(1+Inputs!$C$26)</f>
-        <v>1215</v>
+        <v>847.46249999999998</v>
       </c>
       <c r="D13" s="10">
         <f>IFERROR(C13/$C$16,0)</f>
-        <v>0.40298507462686567</v>
+        <v>0.3434550677061961</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="9">
         <f>C7*Inputs!$C$19*(1-Inputs!$C$24*Inputs!$C$25)*(1+Inputs!$C$26)</f>
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D14" s="10">
         <f>IFERROR(C14/$C$16,0)</f>
-        <v>9.950248756218906E-2</v>
+        <v>0.10942415538230064</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="9">
         <f>C8*Inputs!$C$19*(1-Inputs!$C$24*Inputs!$C$25)*(1+Inputs!$C$26)</f>
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D15" s="10">
         <f>IFERROR(C15/$C$16,0)</f>
-        <v>0.49751243781094528</v>
+        <v>0.54712077691150318</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="12">
         <f>SUM(C13:C15)</f>
-        <v>3015</v>
+        <v>2467.4625000000001</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
@@ -1149,43 +1149,43 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="28">
         <f>$C$16</f>
-        <v>3015</v>
+        <v>2467.4625000000001</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="28">
         <f>$C$16*12</f>
-        <v>36180</v>
+        <v>29609.550000000003</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="29">
         <f>IFERROR($C$16/Inputs!$C$12,0)</f>
-        <v>6.0299999999999999E-2</v>
+        <v>4.9349250000000004E-2</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="30">
         <f>IFERROR($C$16/Inputs!$C$12*1000,0)</f>
-        <v>60.3</v>
+        <v>49.349250000000005</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1194,18 +1194,18 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="14">
         <f>(C6*Inputs!$C$18+C7*Inputs!$C$19+C8*Inputs!$C$19)*(1+Inputs!$C$26)</f>
@@ -1222,58 +1222,58 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="14">
         <f>(C6*Inputs!$C$18*((1-Inputs!$C$22)+Inputs!$C$22*Inputs!$C$23)+C7*Inputs!$C$19+C8*Inputs!$C$19)*(1+Inputs!$C$26)</f>
-        <v>3015</v>
+        <v>2741.625</v>
       </c>
       <c r="D27" s="9">
         <f>$C$26-C27</f>
-        <v>0</v>
+        <v>273.375</v>
       </c>
       <c r="E27" s="15">
         <f>IFERROR(($C$26-C27)/$C$26,0)</f>
-        <v>0</v>
+        <v>9.0671641791044782E-2</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="14">
         <f>(C6*Inputs!$C$18+C7*Inputs!$C$19+C8*Inputs!$C$19)*(1-Inputs!$C$24*Inputs!$C$25)*(1+Inputs!$C$26)</f>
-        <v>3015</v>
+        <v>2713.5</v>
       </c>
       <c r="D28" s="9">
         <f>$C$26-C28</f>
-        <v>0</v>
+        <v>301.5</v>
       </c>
       <c r="E28" s="15">
         <f>IFERROR(($C$26-C28)/$C$26,0)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="16">
         <f>$C$16</f>
-        <v>3015</v>
+        <v>2467.4625000000001</v>
       </c>
       <c r="D29" s="17">
         <f>$C$26-C29</f>
-        <v>0</v>
+        <v>547.53749999999991</v>
       </c>
       <c r="E29" s="18">
         <f>IFERROR(($C$26-C29)/$C$26,0)</f>
-        <v>0</v>
+        <v>0.18160447761194026</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1282,18 +1282,18 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C32" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="19">
         <f>Inputs!$C$12*0.5</f>
@@ -1301,16 +1301,16 @@
       </c>
       <c r="D33" s="14">
         <f>$C$16*0.5</f>
-        <v>1507.5</v>
+        <v>1233.73125</v>
       </c>
       <c r="E33" s="14">
         <f>$C$16*0.5*12</f>
-        <v>18090</v>
+        <v>14804.775000000001</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="19">
         <f>Inputs!$C$12*1</f>
@@ -1318,16 +1318,16 @@
       </c>
       <c r="D34" s="14">
         <f>$C$16*1</f>
-        <v>3015</v>
+        <v>2467.4625000000001</v>
       </c>
       <c r="E34" s="14">
         <f>$C$16*1*12</f>
-        <v>36180</v>
+        <v>29609.550000000003</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="19">
         <f>Inputs!$C$12*2</f>
@@ -1335,16 +1335,16 @@
       </c>
       <c r="D35" s="14">
         <f>$C$16*2</f>
-        <v>6030</v>
+        <v>4934.9250000000002</v>
       </c>
       <c r="E35" s="14">
         <f>$C$16*2*12</f>
-        <v>72360</v>
+        <v>59219.100000000006</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="19">
         <f>Inputs!$C$12*3</f>
@@ -1352,16 +1352,16 @@
       </c>
       <c r="D36" s="14">
         <f>$C$16*3</f>
-        <v>9045</v>
+        <v>7402.3875000000007</v>
       </c>
       <c r="E36" s="14">
         <f>$C$16*3*12</f>
-        <v>108540</v>
+        <v>88828.650000000009</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -1390,152 +1390,152 @@
   <sheetData>
     <row r="2" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
